--- a/pdf2img/tabel/table_0.xlsx
+++ b/pdf2img/tabel/table_0.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,73 +432,56 @@
       <c r="E1" t="n">
         <v>4</v>
       </c>
-      <c r="F1" t="n">
-        <v>5</v>
-      </c>
-      <c r="G1" t="n">
-        <v>6</v>
-      </c>
-      <c r="H1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I1" t="n">
-        <v>8</v>
-      </c>
-      <c r="J1" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NENE</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NEN</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NES</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>T</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>NE</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>NUNES</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>NEES</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>SSD</t>
-        </is>
-      </c>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
